--- a/data/sample_5_answer.xlsx
+++ b/data/sample_5_answer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\portfolio_kweb\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\port_React\portfolio_kweb\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970655BF-0291-4BF6-839F-E60A2348D9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE19BB03-380F-4E5A-BF70-F5B9C470E592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="12984" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="正解" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>設問</t>
   </si>
@@ -44,18 +44,20 @@
     <t>正解</t>
   </si>
   <si>
-    <t>名前</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>川田</t>
     <rPh sb="0" eb="2">
       <t>カワダ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>試験名</t>
+  </si>
+  <si>
+    <t>python模擬試験</t>
+  </si>
+  <si>
+    <t>氏名</t>
   </si>
 </sst>
 </file>
@@ -86,7 +88,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -109,45 +111,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -428,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -717,13 +687,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.600000000000001" thickBot="1"/>
-    <row r="13" spans="1:8" ht="18.600000000000001" thickBot="1">
-      <c r="A13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>3</v>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
